--- a/documentos/base-antecipacao-AULA.xlsx
+++ b/documentos/base-antecipacao-AULA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\00.Aula\Aula_2\Aula\Atividade\atividade-antecipacao-inferencia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/766e71cdafb75dcd/Documentos/Projetos_VSCODE/Ciencia_Dados_(2026_2027)/Projetos/Analise_Contas_Bancarias/documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829FA222-A70C-4302-9F34-6DAC5701E49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dados" sheetId="1" r:id="rId1"/>
@@ -270,7 +270,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -303,7 +303,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
